--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/07,09,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/07,09,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\07,09,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E528E3-87DD-4F6A-9C4D-BB1709F89B34}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DAB648-6506-4F63-AFCF-5183BF5F3B0D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -695,11 +695,11 @@
         <v>2</v>
       </c>
       <c r="B8" s="2">
-        <v>8581</v>
+        <v>8781</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2">
-        <v>8581</v>
+        <v>8781</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2">
@@ -799,7 +799,7 @@
       </c>
       <c r="B14" s="4">
         <f>SUM(B2:B13)</f>
-        <v>31325</v>
+        <v>31525</v>
       </c>
       <c r="C14" s="4">
         <f>SUM(C2:C13)</f>
@@ -807,7 +807,7 @@
       </c>
       <c r="D14" s="4">
         <f>SUM(D2:D13)</f>
-        <v>15433</v>
+        <v>15633</v>
       </c>
       <c r="E14" s="4">
         <f>SUM(E2:E13)</f>
@@ -843,7 +843,7 @@
       </c>
       <c r="D17" s="3">
         <f t="shared" ref="D17:E17" si="2">IF(ROUNDUP(D14/500,0)&gt;32,32,ROUNDUP(D14/500,0))</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="3">
         <f t="shared" si="2"/>
